--- a/saidas/comparativo_preselecionados_qtd.xlsx
+++ b/saidas/comparativo_preselecionados_qtd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>Modelo</t>
   </si>
@@ -52,28 +52,61 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
+    <t>DTR</t>
+  </si>
+  <si>
     <t>SE(LINE)+SE(SGDR)+ABR</t>
   </si>
   <si>
+    <t>SS+POLY+DTR</t>
+  </si>
+  <si>
+    <t>SPct+ABR</t>
+  </si>
+  <si>
+    <t>SE(ABR)+MAS+OHE+ABR</t>
+  </si>
+  <si>
     <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
   </si>
   <si>
     <t>87/211</t>
   </si>
   <si>
+    <t>81/211</t>
+  </si>
+  <si>
     <t>88/211</t>
   </si>
   <si>
-    <t>83/211</t>
+    <t>73/211</t>
+  </si>
+  <si>
+    <t>85/211</t>
+  </si>
+  <si>
+    <t>96/211</t>
   </si>
   <si>
     <t>152/211</t>
   </si>
   <si>
-    <t>147/211</t>
-  </si>
-  <si>
-    <t>140/211</t>
+    <t>146/211</t>
+  </si>
+  <si>
+    <t>158/211</t>
+  </si>
+  <si>
+    <t>153/211</t>
+  </si>
+  <si>
+    <t>154/211</t>
+  </si>
+  <si>
+    <t>156/211</t>
+  </si>
+  <si>
+    <t>144/211</t>
   </si>
   <si>
     <t>211/211</t>
@@ -434,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -477,7 +510,7 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>7.89</v>
@@ -498,13 +531,13 @@
         <v>34.06</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -512,34 +545,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>7.79</v>
+        <v>7.44</v>
       </c>
       <c r="D3">
-        <v>10.06</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E3">
-        <v>0.317</v>
+        <v>0.338</v>
       </c>
       <c r="F3">
-        <v>9.1</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G3">
-        <v>277.2</v>
+        <v>259.3</v>
       </c>
       <c r="H3">
-        <v>34.24</v>
+        <v>28.64</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -547,34 +580,174 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>8.039999999999999</v>
+        <v>7.41</v>
       </c>
       <c r="D4">
-        <v>9.98</v>
+        <v>9.49</v>
       </c>
       <c r="E4">
-        <v>0.319</v>
+        <v>0.345</v>
       </c>
       <c r="F4">
-        <v>9.300000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="G4">
-        <v>276.8</v>
+        <v>264.9</v>
       </c>
       <c r="H4">
-        <v>28.6</v>
+        <v>31.26</v>
       </c>
       <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>7.71</v>
+      </c>
+      <c r="D5">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="E5">
+        <v>0.318</v>
+      </c>
+      <c r="F5">
+        <v>70.5</v>
+      </c>
+      <c r="G5">
+        <v>268.1</v>
+      </c>
+      <c r="H5">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>7.47</v>
+      </c>
+      <c r="D6">
+        <v>9.59</v>
+      </c>
+      <c r="E6">
+        <v>0.336</v>
+      </c>
+      <c r="F6">
+        <v>61</v>
+      </c>
+      <c r="G6">
+        <v>266.6</v>
+      </c>
+      <c r="H6">
+        <v>31.26</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>7.32</v>
+      </c>
+      <c r="D7">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.328</v>
+      </c>
+      <c r="F7">
+        <v>43.7</v>
+      </c>
+      <c r="G7">
+        <v>271.6</v>
+      </c>
+      <c r="H7">
+        <v>34.42</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>7.67</v>
+      </c>
+      <c r="D8">
+        <v>9.73</v>
+      </c>
+      <c r="E8">
+        <v>0.311</v>
+      </c>
+      <c r="F8">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G8">
+        <v>269.6</v>
+      </c>
+      <c r="H8">
+        <v>29.6</v>
+      </c>
+      <c r="I8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/saidas/comparativo_preselecionados_qtd.xlsx
+++ b/saidas/comparativo_preselecionados_qtd.xlsx
@@ -52,6 +52,9 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
+    <t>SARIMA</t>
+  </si>
+  <si>
     <t>DTR</t>
   </si>
   <si>
@@ -64,15 +67,15 @@
     <t>SPct+ABR</t>
   </si>
   <si>
-    <t>SE(ABR)+MAS+OHE+ABR</t>
-  </si>
-  <si>
     <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
   </si>
   <si>
     <t>87/211</t>
   </si>
   <si>
+    <t>84/211</t>
+  </si>
+  <si>
     <t>81/211</t>
   </si>
   <si>
@@ -85,12 +88,12 @@
     <t>85/211</t>
   </si>
   <si>
-    <t>96/211</t>
-  </si>
-  <si>
     <t>152/211</t>
   </si>
   <si>
+    <t>164/211</t>
+  </si>
+  <si>
     <t>146/211</t>
   </si>
   <si>
@@ -101,9 +104,6 @@
   </si>
   <si>
     <t>154/211</t>
-  </si>
-  <si>
-    <t>156/211</t>
   </si>
   <si>
     <t>144/211</t>
@@ -510,7 +510,7 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>7.89</v>
@@ -548,22 +548,22 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>7.44</v>
+        <v>7.16</v>
       </c>
       <c r="D3">
-        <v>9.359999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="E3">
-        <v>0.338</v>
+        <v>0.422</v>
       </c>
       <c r="F3">
-        <v>85.59999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="G3">
-        <v>259.3</v>
+        <v>254.6</v>
       </c>
       <c r="H3">
-        <v>28.64</v>
+        <v>30.6</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -583,22 +583,22 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>7.41</v>
+        <v>7.44</v>
       </c>
       <c r="D4">
-        <v>9.49</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E4">
-        <v>0.345</v>
+        <v>0.338</v>
       </c>
       <c r="F4">
-        <v>59.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="G4">
-        <v>264.9</v>
+        <v>259.3</v>
       </c>
       <c r="H4">
-        <v>31.26</v>
+        <v>28.64</v>
       </c>
       <c r="I4" t="s">
         <v>20</v>
@@ -618,22 +618,22 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>7.71</v>
+        <v>7.41</v>
       </c>
       <c r="D5">
-        <v>9.539999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="E5">
-        <v>0.318</v>
+        <v>0.345</v>
       </c>
       <c r="F5">
-        <v>70.5</v>
+        <v>59.6</v>
       </c>
       <c r="G5">
-        <v>268.1</v>
+        <v>264.9</v>
       </c>
       <c r="H5">
-        <v>31</v>
+        <v>31.26</v>
       </c>
       <c r="I5" t="s">
         <v>21</v>
@@ -653,22 +653,22 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>7.47</v>
+        <v>7.71</v>
       </c>
       <c r="D6">
-        <v>9.59</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="E6">
-        <v>0.336</v>
+        <v>0.318</v>
       </c>
       <c r="F6">
-        <v>61</v>
+        <v>70.5</v>
       </c>
       <c r="G6">
-        <v>266.6</v>
+        <v>268.1</v>
       </c>
       <c r="H6">
-        <v>31.26</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
@@ -688,22 +688,22 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>7.32</v>
+        <v>7.47</v>
       </c>
       <c r="D7">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="E7">
-        <v>0.328</v>
+        <v>0.336</v>
       </c>
       <c r="F7">
-        <v>43.7</v>
+        <v>61</v>
       </c>
       <c r="G7">
-        <v>271.6</v>
+        <v>266.6</v>
       </c>
       <c r="H7">
-        <v>34.42</v>
+        <v>31.26</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
@@ -720,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
         <v>7.67</v>
@@ -741,7 +741,7 @@
         <v>29.6</v>
       </c>
       <c r="I8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" t="s">
         <v>30</v>

--- a/saidas/comparativo_preselecionados_qtd.xlsx
+++ b/saidas/comparativo_preselecionados_qtd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Modelo</t>
   </si>
@@ -52,64 +52,49 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
+    <t>SE(LINE)+SE(SGDR)+ABR</t>
+  </si>
+  <si>
+    <t>SPct+ABR</t>
+  </si>
+  <si>
     <t>SARIMA</t>
   </si>
   <si>
-    <t>DTR</t>
-  </si>
-  <si>
-    <t>SE(LINE)+SE(SGDR)+ABR</t>
-  </si>
-  <si>
-    <t>SS+POLY+DTR</t>
-  </si>
-  <si>
-    <t>SPct+ABR</t>
-  </si>
-  <si>
     <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
   </si>
   <si>
     <t>87/211</t>
   </si>
   <si>
-    <t>84/211</t>
-  </si>
-  <si>
-    <t>81/211</t>
-  </si>
-  <si>
     <t>88/211</t>
   </si>
   <si>
-    <t>73/211</t>
-  </si>
-  <si>
     <t>85/211</t>
   </si>
   <si>
+    <t>98/211</t>
+  </si>
+  <si>
     <t>152/211</t>
   </si>
   <si>
-    <t>164/211</t>
-  </si>
-  <si>
-    <t>146/211</t>
-  </si>
-  <si>
     <t>158/211</t>
   </si>
   <si>
-    <t>153/211</t>
-  </si>
-  <si>
     <t>154/211</t>
   </si>
   <si>
+    <t>160/211</t>
+  </si>
+  <si>
     <t>144/211</t>
   </si>
   <si>
     <t>211/211</t>
+  </si>
+  <si>
+    <t>210/211</t>
   </si>
 </sst>
 </file>
@@ -467,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -531,13 +516,13 @@
         <v>34.06</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -545,34 +530,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>7.16</v>
+        <v>7.41</v>
       </c>
       <c r="D3">
-        <v>9.01</v>
+        <v>9.49</v>
       </c>
       <c r="E3">
-        <v>0.422</v>
+        <v>0.345</v>
       </c>
       <c r="F3">
-        <v>16.2</v>
+        <v>59.6</v>
       </c>
       <c r="G3">
-        <v>254.6</v>
+        <v>264.9</v>
       </c>
       <c r="H3">
-        <v>30.6</v>
+        <v>31.26</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
         <v>25</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -580,34 +565,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>7.44</v>
+        <v>7.47</v>
       </c>
       <c r="D4">
-        <v>9.359999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="E4">
-        <v>0.338</v>
+        <v>0.336</v>
       </c>
       <c r="F4">
-        <v>85.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="G4">
-        <v>259.3</v>
+        <v>266.6</v>
       </c>
       <c r="H4">
-        <v>28.64</v>
+        <v>31.26</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -615,139 +600,104 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>7.41</v>
+        <v>7.16</v>
       </c>
       <c r="D5">
-        <v>9.49</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E5">
         <v>0.345</v>
       </c>
       <c r="F5">
-        <v>59.6</v>
+        <v>23.9</v>
       </c>
       <c r="G5">
-        <v>264.9</v>
+        <v>270.6</v>
       </c>
       <c r="H5">
-        <v>31.26</v>
+        <v>52.1</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>7.71</v>
+        <v>7.16</v>
       </c>
       <c r="D6">
-        <v>9.539999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E6">
-        <v>0.318</v>
+        <v>0.345</v>
       </c>
       <c r="F6">
-        <v>70.5</v>
+        <v>23.9</v>
       </c>
       <c r="G6">
-        <v>268.1</v>
+        <v>270.6</v>
       </c>
       <c r="H6">
-        <v>31</v>
+        <v>52.1</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>7.47</v>
+        <v>7.67</v>
       </c>
       <c r="D7">
-        <v>9.59</v>
+        <v>9.73</v>
       </c>
       <c r="E7">
-        <v>0.336</v>
+        <v>0.311</v>
       </c>
       <c r="F7">
-        <v>61</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G7">
-        <v>266.6</v>
+        <v>269.6</v>
       </c>
       <c r="H7">
-        <v>31.26</v>
+        <v>29.6</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>7.67</v>
-      </c>
-      <c r="D8">
-        <v>9.73</v>
-      </c>
-      <c r="E8">
-        <v>0.311</v>
-      </c>
-      <c r="F8">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="G8">
-        <v>269.6</v>
-      </c>
-      <c r="H8">
-        <v>29.6</v>
-      </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/saidas/comparativo_preselecionados_qtd.xlsx
+++ b/saidas/comparativo_preselecionados_qtd.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
   <si>
     <t>Modelo</t>
   </si>
@@ -52,49 +52,70 @@
     <t>Pipeline Antiga em Producao</t>
   </si>
   <si>
+    <t>ABR-2</t>
+  </si>
+  <si>
     <t>SE(LINE)+SE(SGDR)+ABR</t>
   </si>
   <si>
-    <t>SPct+ABR</t>
+    <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
+  </si>
+  <si>
+    <t>VotingRegressor (RandomForest + XGBoost + ExtraTrees)</t>
+  </si>
+  <si>
+    <t>SE(LINE)+ABR</t>
   </si>
   <si>
     <t>SARIMA</t>
   </si>
   <si>
-    <t>SE(ETR)+MMS+BIN+SE(ELAS)+ABR</t>
-  </si>
-  <si>
-    <t>87/211</t>
-  </si>
-  <si>
-    <t>88/211</t>
-  </si>
-  <si>
-    <t>85/211</t>
-  </si>
-  <si>
-    <t>98/211</t>
-  </si>
-  <si>
-    <t>152/211</t>
-  </si>
-  <si>
-    <t>158/211</t>
-  </si>
-  <si>
-    <t>154/211</t>
-  </si>
-  <si>
-    <t>160/211</t>
-  </si>
-  <si>
-    <t>144/211</t>
-  </si>
-  <si>
-    <t>211/211</t>
-  </si>
-  <si>
-    <t>210/211</t>
+    <t>108/262</t>
+  </si>
+  <si>
+    <t>112/262</t>
+  </si>
+  <si>
+    <t>107/262</t>
+  </si>
+  <si>
+    <t>111/262</t>
+  </si>
+  <si>
+    <t>102/262</t>
+  </si>
+  <si>
+    <t>104/262</t>
+  </si>
+  <si>
+    <t>116/262</t>
+  </si>
+  <si>
+    <t>186/262</t>
+  </si>
+  <si>
+    <t>190/262</t>
+  </si>
+  <si>
+    <t>191/262</t>
+  </si>
+  <si>
+    <t>185/262</t>
+  </si>
+  <si>
+    <t>192/262</t>
+  </si>
+  <si>
+    <t>183/262</t>
+  </si>
+  <si>
+    <t>188/262</t>
+  </si>
+  <si>
+    <t>262/262</t>
+  </si>
+  <si>
+    <t>261/262</t>
   </si>
 </sst>
 </file>
@@ -452,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -495,34 +516,34 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>7.89</v>
+        <v>8.01</v>
       </c>
       <c r="D2">
-        <v>9.880000000000001</v>
+        <v>10.23</v>
       </c>
       <c r="E2">
-        <v>0.313</v>
+        <v>0.365</v>
       </c>
       <c r="F2">
-        <v>40.5</v>
+        <v>22.2</v>
       </c>
       <c r="G2">
-        <v>275.2</v>
+        <v>276.8</v>
       </c>
       <c r="H2">
-        <v>34.06</v>
+        <v>35.74</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -530,34 +551,34 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>7.41</v>
+        <v>7.56</v>
       </c>
       <c r="D3">
-        <v>9.49</v>
+        <v>9.81</v>
       </c>
       <c r="E3">
-        <v>0.345</v>
+        <v>0.411</v>
       </c>
       <c r="F3">
-        <v>59.6</v>
+        <v>34.5</v>
       </c>
       <c r="G3">
-        <v>264.9</v>
+        <v>265.1</v>
       </c>
       <c r="H3">
-        <v>31.26</v>
+        <v>31.99</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -565,34 +586,34 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>7.47</v>
+        <v>7.63</v>
       </c>
       <c r="D4">
-        <v>9.59</v>
+        <v>9.84</v>
       </c>
       <c r="E4">
-        <v>0.336</v>
+        <v>0.399</v>
       </c>
       <c r="F4">
-        <v>61</v>
+        <v>37.7</v>
       </c>
       <c r="G4">
-        <v>266.6</v>
+        <v>267.3</v>
       </c>
       <c r="H4">
-        <v>31.26</v>
+        <v>31.45</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -600,104 +621,139 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>7.16</v>
+        <v>7.68</v>
       </c>
       <c r="D5">
-        <v>9.609999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="E5">
-        <v>0.345</v>
+        <v>0.386</v>
       </c>
       <c r="F5">
-        <v>23.9</v>
+        <v>43.9</v>
       </c>
       <c r="G5">
-        <v>270.6</v>
+        <v>269.3</v>
       </c>
       <c r="H5">
-        <v>52.1</v>
+        <v>29.14</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>7.16</v>
+        <v>7.7</v>
       </c>
       <c r="D6">
-        <v>9.609999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="E6">
-        <v>0.345</v>
+        <v>0.358</v>
       </c>
       <c r="F6">
-        <v>23.9</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>270.6</v>
+        <v>273.5</v>
       </c>
       <c r="H6">
-        <v>52.1</v>
+        <v>32.5</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="D7">
-        <v>9.73</v>
+        <v>10.11</v>
       </c>
       <c r="E7">
-        <v>0.311</v>
+        <v>0.365</v>
       </c>
       <c r="F7">
-        <v>69.90000000000001</v>
+        <v>36.7</v>
       </c>
       <c r="G7">
-        <v>269.6</v>
+        <v>275</v>
       </c>
       <c r="H7">
-        <v>29.6</v>
+        <v>33.64</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>7.62</v>
+      </c>
+      <c r="D8">
+        <v>10.13</v>
+      </c>
+      <c r="E8">
+        <v>0.362</v>
+      </c>
+      <c r="F8">
+        <v>13.6</v>
+      </c>
+      <c r="G8">
+        <v>277.9</v>
+      </c>
+      <c r="H8">
+        <v>50.83</v>
+      </c>
+      <c r="I8" t="s">
         <v>24</v>
       </c>
-      <c r="K7" t="s">
-        <v>25</v>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
